--- a/config/generated/templates/CharacterStat.xlsx
+++ b/config/generated/templates/CharacterStat.xlsx
@@ -31,16 +31,16 @@
     <t>@key</t>
   </si>
   <si>
-    <t>@scope</t>
-  </si>
-  <si>
-    <t>all</t>
+    <t>@groups</t>
+  </si>
+  <si>
+    <t>common</t>
   </si>
   <si>
     <t>@schema</t>
   </si>
   <si>
-    <t>70c1b12321d9ed65</t>
+    <t>bb5bc5034c7367d7</t>
   </si>
   <si>
     <t>#name</t>
@@ -82,7 +82,7 @@
     <t>string</t>
   </si>
   <si>
-    <t>#scope</t>
+    <t>#groups</t>
   </si>
   <si>
     <t>#input</t>
